--- a/users/cc.xlsx
+++ b/users/cc.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="PO Accounts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="9">
   <si>
     <t>commaccn@gmail.com</t>
   </si>
@@ -33,6 +34,15 @@
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>userinfo789789</t>
+  </si>
+  <si>
+    <t>userinfo5566</t>
+  </si>
+  <si>
+    <t>userinfo6699</t>
   </si>
 </sst>
 </file>
@@ -589,4 +599,68 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>